--- a/backend/data/financials_by_company/002434.SZ.xlsx
+++ b/backend/data/financials_by_company/002434.SZ.xlsx
@@ -4103,172 +4103,172 @@
       </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Zhejiang Wanliyang Co., Ltd. engages in the research and development, production, and sale of automotive transmissions and transmission/drive system products for new energy vehicles in China and internationally. It offers automotive transmission products, including passenger car transmissions and commercial vehicle transmissions, which are used in passenger cars, SUVs, MPVs, commercial vehicles, including logistics transportation trucks, low speed &amp; heavy-duty dumpers, buses, municipal vehicles, school buses, pickups. The company also offers launched CVT for tractors, agricultural machinery power shifting system, humanoid robot transmission device, electric drive system of construction machine; precision mechanical components providing quality and cost parts such as housings, gears, differentials, synchronizers, and other products. The company was formerly known as Zhejiang Wanliyang Transmission Company Ltd. and changed its name to Zhejiang Wanliyang Co., Ltd. in January 2016. Zhejiang Wanliyang Co., Ltd. was founded in 2003 and is headquartered in Jinhua, China.</t>
+          <t>Zhejiang Wanliyang Co., Ltd. engages in the research and development, production, and sale of automotive transmissions and transmission/drive system products for new energy vehicles in China and internationally. It offers automotive transmission products, including passenger car transmissions and commercial vehicle transmissions, which are used in passenger cars, SUVs, MPVs, commercial vehicles, including logistics transportation trucks, low speed and heavy-duty dumpers, buses, municipal vehicles, school buses, pickups. The company also offers launched CVT for tractors, agricultural machinery power shifting system, humanoid robot transmission device, electric drive system of construction machine; precision mechanical components providing quality and cost parts such as housings, gears, differentials, synchronizers, and other products. The company was formerly known as Zhejiang Wanliyang Transmission Company Ltd. and changed its name to Zhejiang Wanliyang Co., Ltd. in January 2016. Zhejiang Wanliyang Co., Ltd. was founded in 2003 and is headquartered in Jinhua, China.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4368,37 +4368,37 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>6.78</v>
+        <v>6.06</v>
       </c>
       <c r="U2" t="n">
-        <v>6.88</v>
+        <v>6.12</v>
       </c>
       <c r="V2" t="n">
-        <v>6.47</v>
+        <v>6.07</v>
       </c>
       <c r="W2" t="n">
-        <v>6.77</v>
+        <v>6.67</v>
       </c>
       <c r="X2" t="n">
-        <v>6.78</v>
+        <v>6.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.88</v>
+        <v>6.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.47</v>
+        <v>6.07</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.77</v>
+        <v>6.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.47</v>
+        <v>0.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1750291200</v>
+        <v>1782950400</v>
       </c>
       <c r="AE2" t="n">
         <v>0.6667</v>
@@ -4407,43 +4407,43 @@
         <v>2.31</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.716</v>
+        <v>0.735</v>
       </c>
       <c r="AH2" t="n">
-        <v>44.266663</v>
+        <v>44.466667</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.434782</v>
+        <v>14.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20579161</v>
+        <v>28425726</v>
       </c>
       <c r="AK2" t="n">
-        <v>20579161</v>
+        <v>28425726</v>
       </c>
       <c r="AL2" t="n">
-        <v>21081756</v>
+        <v>21956961</v>
       </c>
       <c r="AM2" t="n">
-        <v>25845960</v>
+        <v>18868879</v>
       </c>
       <c r="AN2" t="n">
-        <v>25845960</v>
+        <v>18868879</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.63</v>
+        <v>6.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.64</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8715664384</v>
+        <v>8755042304</v>
       </c>
       <c r="AR2" t="n">
-        <v>8899428000</v>
+        <v>7862474000</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.47</v>
+        <v>5.77</v>
       </c>
       <c r="AT2" t="n">
         <v>11.31</v>
@@ -4455,19 +4455,19 @@
         <v>1.883333</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.7289042</v>
+        <v>1.7367154</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.4524</v>
+        <v>7.1168</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.805949999999999</v>
+        <v>8.664949999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.05</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0073746312</v>
+        <v>0.008250825</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -4478,22 +4478,22 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>9317023744</v>
+        <v>9356401664</v>
       </c>
       <c r="BE2" t="n">
         <v>0.040510003</v>
       </c>
       <c r="BF2" t="n">
-        <v>649723874</v>
+        <v>696058654</v>
       </c>
       <c r="BG2" t="n">
         <v>1312600000</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.43582</v>
+        <v>0.43576</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.14124</v>
+        <v>0.14123</v>
       </c>
       <c r="BJ2" t="n">
         <v>1312600000</v>
@@ -4502,7 +4502,7 @@
         <v>4.512</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.4716312</v>
+        <v>1.4782802</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4534,22 +4534,22 @@
         <v>1460332800</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.848</v>
+        <v>1.856</v>
       </c>
       <c r="BW2" t="n">
-        <v>17.955</v>
+        <v>18.031</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.0029411912</v>
+        <v>-0.16413796</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>1750291200</v>
+        <v>1782950400</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
@@ -4670,128 +4670,128 @@
         </is>
       </c>
       <c r="DH2" t="n">
-        <v>1782111879</v>
+        <v>1783062285</v>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>finmb_106528429</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1651143540</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1651233600</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.44679976</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.06278098999999999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-1.9949503</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.23023216</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1276824600000</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.61000013</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>6.07 - 6.67</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>21956961</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.9000001</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.15597922</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>5.77 - 11.31</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-4.6400003</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.41025642</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-16.413795</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
           <t>ZHEJIANG WANLIYANG CO LTD</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EN2" t="n">
+        <v>10.066009</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="EP2" t="inlineStr">
         <is>
           <t>Zhejiang Wanliyang Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>finmb_106528429</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-2.0649018</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>21081756</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.17000008</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.026275128</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>6.47 - 11.31</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-4.6700006</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.41290897</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.29411912</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1651143540</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1651233600</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.8124003400000001</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.1090119</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-2.1659503</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-0.24596441</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1276824600000</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.14000034</v>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>6.47 - 6.77</t>
         </is>
       </c>
       <c r="EQ2" t="inlineStr"/>
